--- a/星形图输出/星形图维度得分汇总.xlsx
+++ b/星形图输出/星形图维度得分汇总.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,27 +459,911 @@
           <t>活动参与与公共活力（B5）</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>生成时间</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>运行批次</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>高崎小学入口</t>
+          <t>主要街巷道路1</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>3</v>
       </c>
       <c r="C2" t="n">
+        <v>2.83333333333333</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.33333333333333</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4.16666666666667</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-07-08 14:34:45</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>20260708_143445</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>主要街巷道路2(林氏宗祠)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C3" t="n">
         <v>4.5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-07-08 15:50:11</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20260708_155011</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>万寿宫</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.83333333333333</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.33333333333333</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.16666666666667</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.125</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-07-09 10:35:58</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>20260709_103558</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>林氏宗祠</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.16666666666667</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.16666666666667</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.66666666666667</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-07-09 15:57:18</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>20260709_155718</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>高崎炮台</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.83333333333333</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:53:44</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>20260709_165344</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>林氏宗祠后方空间</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.83333333333333</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.66666666666667</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:32:59</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>20260710_103259</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>高崎幼儿园</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.66666666666667</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.83333333333333</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:49:58</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>20260710_104958</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>涵洞</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.33333333333333</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.66666666666667</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:23:00</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>20260710_112300</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>天桥</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.33333333333333</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.66666666666667</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.33333333333333</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-07-10 13:13:17</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>20260710_131317</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>(外来型)凤凰木入口</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.33333333333333</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.875</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:08:05</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>20260714_160805</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>(在地型)主要街巷1(万寿宫)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.83333333333333</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.33333333333333</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4.33333333333333</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:19:54</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>20260714_161954</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>(在地型)主要街巷道路2(林氏宗祠)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.66666666666667</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:30:42</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>20260714_163042</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>(在地型)万寿宫</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4.33333333333333</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.33333333333333</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-07-15 10:09:42</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>20260715_100942</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>(在地型)林氏宗祠</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.66666666666667</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.875</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-07-15 10:30:08</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>20260715_103008</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>(外来型)高企炮台</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.83333333333333</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:01:19</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>20260715_110119</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>(外来型)万寿宫</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.66666666666667</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.33333333333333</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-07-15 14:56:39</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>20260715_145639</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>(外来型)林氏宗祠</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.16666666666667</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.83333333333333</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.83333333333333</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-07-15 15:15:45</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>20260715_151545</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>(外来型)高崎小学入口</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.66666666666667</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.83333333333333</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-07-15 15:24:29</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>20260715_152429</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>(在地型)高崎小学入口</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.83333333333333</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-07-15 15:46:07</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>20260715_154607</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>(外来型)主要街巷1(万寿宫)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4.16666666666667</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.16666666666667</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4.33333333333333</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:31:31</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>20260715_163131</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>(外来型)主要街巷道路2(林氏宗祠)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4.66666666666667</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.66666666666667</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.83333333333333</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:30:11</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>20260716_103011</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>(外来型)林氏宗祠后方空间</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4.83333333333333</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.33333333333333</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.83333333333333</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-07-16 11:20:47</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>20260716_112047</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>(在地型)林氏宗祠后方空间</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4.16666666666667</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.83333333333333</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.66666666666667</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-07-16 11:23:06</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>20260716_112306</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>(在地型)高崎幼儿园</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4.66666666666667</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.83333333333333</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:53:31</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>20260716_135331</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>(外来型)高崎幼儿园</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.16666666666667</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:59:17</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>20260716_135917</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>(在地型)涵洞</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.33333333333333</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.66666666666667</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:19:21</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>20260716_151921</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>(外来型)涵洞</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:31:09</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>20260716_153109</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>(外来型)天桥</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D29" t="n">
         <v>3.333333333333333</v>
       </c>
-      <c r="E2" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:45:56</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>20260716_154556</t>
+        </is>
       </c>
     </row>
   </sheetData>
